--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6507" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6507" uniqueCount="652">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -492,6 +492,10 @@
     <t>Procedure.extension.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -550,14 +554,10 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Procedure.extension:difficulte</t>
@@ -961,10 +961,6 @@
     <t>Procedure.recorder.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Procedure.recorder.extension</t>
   </si>
   <si>
@@ -1033,9 +1029,6 @@
   </si>
   <si>
     <t>Procedure.recorder.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>AUT</t>
@@ -3643,7 +3636,7 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>138</v>
@@ -3689,13 +3682,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3746,7 +3739,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3755,7 +3748,7 @@
         <v>87</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>77</v>
@@ -3764,7 +3757,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -3775,10 +3768,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3849,7 +3842,7 @@
         <v>135</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
@@ -3858,7 +3851,7 @@
         <v>136</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3887,10 +3880,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3916,13 +3909,13 @@
         <v>101</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3930,7 +3923,7 @@
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>77</v>
@@ -3972,7 +3965,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>87</v>
@@ -4001,10 +3994,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4027,13 +4020,13 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4084,7 +4077,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4093,7 +4086,7 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>99</v>
@@ -5955,13 +5948,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6012,7 +6005,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6030,7 +6023,7 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -6041,10 +6034,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6070,10 +6063,10 @@
         <v>132</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>183</v>
@@ -6117,7 +6110,7 @@
         <v>135</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>77</v>
@@ -6126,7 +6119,7 @@
         <v>136</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6144,7 +6137,7 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -6155,13 +6148,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C34" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>77</v>
@@ -6183,13 +6176,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6240,7 +6233,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6269,10 +6262,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6295,13 +6288,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6352,7 +6345,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6370,7 +6363,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -6381,10 +6374,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6392,7 +6385,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>79</v>
@@ -6455,7 +6448,7 @@
         <v>135</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
@@ -6464,7 +6457,7 @@
         <v>136</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6493,13 +6486,13 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C37" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>77</v>
@@ -6578,7 +6571,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6607,10 +6600,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6633,13 +6626,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6690,7 +6683,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6708,7 +6701,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6719,10 +6712,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6793,7 +6786,7 @@
         <v>135</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
@@ -6802,7 +6795,7 @@
         <v>136</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6831,10 +6824,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6860,13 +6853,13 @@
         <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6874,7 +6867,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>77</v>
@@ -6916,7 +6909,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>87</v>
@@ -6945,10 +6938,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6974,10 +6967,10 @@
         <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6989,7 +6982,7 @@
         <v>77</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>77</v>
@@ -7008,7 +7001,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -7026,7 +7019,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7055,13 +7048,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>77</v>
@@ -7086,7 +7079,7 @@
         <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M42" t="s" s="2">
         <v>134</v>
@@ -7140,7 +7133,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7169,10 +7162,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7195,13 +7188,13 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7252,7 +7245,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7270,7 +7263,7 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -7281,10 +7274,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7355,7 +7348,7 @@
         <v>135</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>77</v>
@@ -7364,7 +7357,7 @@
         <v>136</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7393,10 +7386,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7422,13 +7415,13 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7436,7 +7429,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>77</v>
@@ -7478,7 +7471,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>87</v>
@@ -7507,10 +7500,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7536,10 +7529,10 @@
         <v>239</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7590,7 +7583,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7619,13 +7612,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -7704,7 +7697,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7733,10 +7726,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7759,13 +7752,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7816,7 +7809,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7834,7 +7827,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7845,10 +7838,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7919,7 +7912,7 @@
         <v>135</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>77</v>
@@ -7928,7 +7921,7 @@
         <v>136</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7957,10 +7950,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7986,13 +7979,13 @@
         <v>101</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8000,7 +7993,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>77</v>
@@ -8042,7 +8035,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>87</v>
@@ -8071,10 +8064,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8097,13 +8090,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8154,7 +8147,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8183,10 +8176,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8212,13 +8205,13 @@
         <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8226,7 +8219,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>77</v>
@@ -8268,7 +8261,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>87</v>
@@ -8297,10 +8290,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8323,13 +8316,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8380,7 +8373,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8409,10 +8402,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8435,16 +8428,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8494,7 +8487,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8503,7 +8496,7 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>99</v>
@@ -8523,10 +8516,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8552,13 +8545,13 @@
         <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8584,31 +8577,31 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="Y55" t="s" s="2">
+      <c r="AA55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8637,10 +8630,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8666,13 +8659,13 @@
         <v>187</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8722,7 +8715,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8740,7 +8733,7 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8751,10 +8744,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8777,16 +8770,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8836,7 +8829,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8865,10 +8858,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8894,10 +8887,10 @@
         <v>294</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8948,7 +8941,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8966,10 +8959,10 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8977,10 +8970,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9003,13 +8996,13 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9060,7 +9053,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9075,10 +9068,10 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -9089,10 +9082,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9115,13 +9108,13 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9172,7 +9165,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9190,7 +9183,7 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -9201,10 +9194,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9230,10 +9223,10 @@
         <v>132</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>183</v>
@@ -9286,7 +9279,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9304,7 +9297,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -9315,14 +9308,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9344,10 +9337,10 @@
         <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>183</v>
@@ -9402,7 +9395,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9431,10 +9424,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9460,14 +9453,14 @@
         <v>239</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9495,10 +9488,10 @@
         <v>243</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9516,7 +9509,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9531,24 +9524,24 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>398</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9571,17 +9564,17 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9630,7 +9623,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>87</v>
@@ -9645,24 +9638,24 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9685,13 +9678,13 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9742,7 +9735,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9760,7 +9753,7 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9771,10 +9764,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9800,10 +9793,10 @@
         <v>132</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>183</v>
@@ -9847,7 +9840,7 @@
         <v>135</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>77</v>
@@ -9856,7 +9849,7 @@
         <v>136</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9874,7 +9867,7 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9885,13 +9878,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B67" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C67" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>77</v>
@@ -9913,13 +9906,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9970,7 +9963,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9999,10 +9992,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10025,13 +10018,13 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10082,7 +10075,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10100,7 +10093,7 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -10111,10 +10104,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10122,7 +10115,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>79</v>
@@ -10185,7 +10178,7 @@
         <v>135</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>77</v>
@@ -10194,7 +10187,7 @@
         <v>136</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10223,13 +10216,13 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>77</v>
@@ -10308,7 +10301,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10337,10 +10330,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10363,13 +10356,13 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10420,7 +10413,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10438,7 +10431,7 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -10449,10 +10442,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10523,7 +10516,7 @@
         <v>135</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>77</v>
@@ -10532,7 +10525,7 @@
         <v>136</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10561,10 +10554,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10590,13 +10583,13 @@
         <v>101</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10604,7 +10597,7 @@
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>77</v>
@@ -10646,7 +10639,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>87</v>
@@ -10675,10 +10668,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10704,10 +10697,10 @@
         <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10719,7 +10712,7 @@
         <v>77</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>77</v>
@@ -10738,7 +10731,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>77</v>
@@ -10756,7 +10749,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10785,13 +10778,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>77</v>
@@ -10816,7 +10809,7 @@
         <v>132</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>134</v>
@@ -10870,7 +10863,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10899,10 +10892,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10925,13 +10918,13 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10982,7 +10975,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11000,7 +10993,7 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -11011,10 +11004,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11085,7 +11078,7 @@
         <v>135</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>77</v>
@@ -11094,7 +11087,7 @@
         <v>136</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11123,10 +11116,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11152,13 +11145,13 @@
         <v>101</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11166,7 +11159,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>77</v>
@@ -11208,7 +11201,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>87</v>
@@ -11237,10 +11230,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11266,10 +11259,10 @@
         <v>239</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11320,7 +11313,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11349,13 +11342,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>77</v>
@@ -11434,7 +11427,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11463,10 +11456,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11489,13 +11482,13 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11546,7 +11539,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11564,7 +11557,7 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -11575,10 +11568,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11649,7 +11642,7 @@
         <v>135</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>77</v>
@@ -11658,7 +11651,7 @@
         <v>136</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11687,10 +11680,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11716,13 +11709,13 @@
         <v>101</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11730,7 +11723,7 @@
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>77</v>
@@ -11772,7 +11765,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>87</v>
@@ -11801,10 +11794,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11827,13 +11820,13 @@
         <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11884,7 +11877,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11913,10 +11906,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11942,13 +11935,13 @@
         <v>101</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11956,7 +11949,7 @@
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>77</v>
@@ -11998,7 +11991,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>87</v>
@@ -12027,10 +12020,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12053,13 +12046,13 @@
         <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12110,7 +12103,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12139,13 +12132,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>77</v>
@@ -12167,13 +12160,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12224,7 +12217,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12253,10 +12246,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12279,13 +12272,13 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12336,7 +12329,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12354,7 +12347,7 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -12365,10 +12358,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12376,7 +12369,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>79</v>
@@ -12439,7 +12432,7 @@
         <v>135</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>77</v>
@@ -12448,7 +12441,7 @@
         <v>136</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12477,13 +12470,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>77</v>
@@ -12562,7 +12555,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12591,10 +12584,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12617,13 +12610,13 @@
         <v>77</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12674,7 +12667,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12692,7 +12685,7 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
@@ -12703,10 +12696,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12777,7 +12770,7 @@
         <v>135</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>77</v>
@@ -12786,7 +12779,7 @@
         <v>136</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12815,10 +12808,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12844,13 +12837,13 @@
         <v>101</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12858,7 +12851,7 @@
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>77</v>
@@ -12900,7 +12893,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>87</v>
@@ -12929,10 +12922,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12958,10 +12951,10 @@
         <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12973,7 +12966,7 @@
         <v>77</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>77</v>
@@ -12992,7 +12985,7 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -13010,7 +13003,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13039,13 +13032,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>77</v>
@@ -13070,7 +13063,7 @@
         <v>132</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M95" t="s" s="2">
         <v>134</v>
@@ -13124,7 +13117,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13153,10 +13146,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13179,13 +13172,13 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13236,7 +13229,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13254,7 +13247,7 @@
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -13265,10 +13258,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13339,7 +13332,7 @@
         <v>135</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>77</v>
@@ -13348,7 +13341,7 @@
         <v>136</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13377,10 +13370,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13406,13 +13399,13 @@
         <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13420,7 +13413,7 @@
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>77</v>
@@ -13462,7 +13455,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -13491,10 +13484,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13520,10 +13513,10 @@
         <v>239</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13574,7 +13567,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13603,13 +13596,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>77</v>
@@ -13688,7 +13681,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13717,10 +13710,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13743,13 +13736,13 @@
         <v>77</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13800,7 +13793,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13818,7 +13811,7 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
@@ -13829,10 +13822,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13903,7 +13896,7 @@
         <v>135</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>77</v>
@@ -13912,7 +13905,7 @@
         <v>136</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13941,10 +13934,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13970,13 +13963,13 @@
         <v>101</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13984,7 +13977,7 @@
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>77</v>
@@ -14026,7 +14019,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>87</v>
@@ -14055,10 +14048,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14081,13 +14074,13 @@
         <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14138,7 +14131,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14167,10 +14160,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14196,13 +14189,13 @@
         <v>101</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14210,7 +14203,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>77</v>
@@ -14252,7 +14245,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>87</v>
@@ -14281,10 +14274,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14307,13 +14300,13 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14364,7 +14357,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14393,13 +14386,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>77</v>
@@ -14421,13 +14414,13 @@
         <v>77</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14478,7 +14471,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14507,10 +14500,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14533,13 +14526,13 @@
         <v>77</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14590,7 +14583,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14608,7 +14601,7 @@
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
@@ -14619,10 +14612,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14630,7 +14623,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>79</v>
@@ -14693,7 +14686,7 @@
         <v>135</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>77</v>
@@ -14702,7 +14695,7 @@
         <v>136</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14731,13 +14724,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>77</v>
@@ -14816,7 +14809,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14845,10 +14838,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14871,13 +14864,13 @@
         <v>77</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14928,7 +14921,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14946,7 +14939,7 @@
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>77</v>
@@ -14957,10 +14950,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15031,7 +15024,7 @@
         <v>135</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>77</v>
@@ -15040,7 +15033,7 @@
         <v>136</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15069,10 +15062,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15098,13 +15091,13 @@
         <v>101</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15112,7 +15105,7 @@
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>77</v>
@@ -15154,7 +15147,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>87</v>
@@ -15183,10 +15176,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15212,10 +15205,10 @@
         <v>107</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15227,7 +15220,7 @@
         <v>77</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>77</v>
@@ -15246,7 +15239,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>77</v>
@@ -15264,7 +15257,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15293,13 +15286,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>77</v>
@@ -15324,7 +15317,7 @@
         <v>132</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M115" t="s" s="2">
         <v>134</v>
@@ -15378,7 +15371,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15407,10 +15400,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15433,13 +15426,13 @@
         <v>77</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15490,7 +15483,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15508,7 +15501,7 @@
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>77</v>
@@ -15519,10 +15512,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15593,7 +15586,7 @@
         <v>135</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>77</v>
@@ -15602,7 +15595,7 @@
         <v>136</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15631,10 +15624,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15660,13 +15653,13 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15674,7 +15667,7 @@
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="S118" t="s" s="2">
         <v>77</v>
@@ -15716,7 +15709,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>87</v>
@@ -15745,10 +15738,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15774,10 +15767,10 @@
         <v>239</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15828,7 +15821,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15857,13 +15850,13 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>77</v>
@@ -15942,7 +15935,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15971,10 +15964,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15997,13 +15990,13 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16054,7 +16047,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16072,7 +16065,7 @@
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -16083,10 +16076,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16157,7 +16150,7 @@
         <v>135</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>77</v>
@@ -16166,7 +16159,7 @@
         <v>136</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16195,10 +16188,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16224,13 +16217,13 @@
         <v>101</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -16238,7 +16231,7 @@
       </c>
       <c r="Q123" s="2"/>
       <c r="R123" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="S123" t="s" s="2">
         <v>77</v>
@@ -16280,7 +16273,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>87</v>
@@ -16309,10 +16302,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16335,13 +16328,13 @@
         <v>77</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16392,7 +16385,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16421,10 +16414,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16450,13 +16443,13 @@
         <v>101</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16464,7 +16457,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>77</v>
@@ -16506,7 +16499,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>87</v>
@@ -16535,10 +16528,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16561,13 +16554,13 @@
         <v>77</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16618,7 +16611,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16647,13 +16640,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>77</v>
@@ -16675,13 +16668,13 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16732,7 +16725,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -16761,10 +16754,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16787,13 +16780,13 @@
         <v>77</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -16844,7 +16837,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -16862,7 +16855,7 @@
         <v>77</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>77</v>
@@ -16873,10 +16866,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16884,7 +16877,7 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>79</v>
@@ -16947,7 +16940,7 @@
         <v>135</v>
       </c>
       <c r="AC129" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD129" t="s" s="2">
         <v>77</v>
@@ -16956,7 +16949,7 @@
         <v>136</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -16985,13 +16978,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>77</v>
@@ -17070,7 +17063,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17099,10 +17092,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17125,13 +17118,13 @@
         <v>77</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17182,7 +17175,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17200,7 +17193,7 @@
         <v>77</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>77</v>
@@ -17211,10 +17204,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17285,7 +17278,7 @@
         <v>135</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>77</v>
@@ -17294,7 +17287,7 @@
         <v>136</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17323,10 +17316,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17352,13 +17345,13 @@
         <v>101</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17366,7 +17359,7 @@
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S133" t="s" s="2">
         <v>77</v>
@@ -17408,7 +17401,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>87</v>
@@ -17437,10 +17430,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17466,10 +17459,10 @@
         <v>107</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -17481,7 +17474,7 @@
         <v>77</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>77</v>
@@ -17500,7 +17493,7 @@
       </c>
       <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>77</v>
@@ -17518,7 +17511,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17547,13 +17540,13 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>77</v>
@@ -17578,7 +17571,7 @@
         <v>132</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M135" t="s" s="2">
         <v>134</v>
@@ -17632,7 +17625,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17661,10 +17654,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17687,13 +17680,13 @@
         <v>77</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -17744,7 +17737,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -17762,7 +17755,7 @@
         <v>77</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>77</v>
@@ -17773,10 +17766,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17847,7 +17840,7 @@
         <v>135</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>77</v>
@@ -17856,7 +17849,7 @@
         <v>136</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -17885,10 +17878,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17914,13 +17907,13 @@
         <v>101</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -17928,7 +17921,7 @@
       </c>
       <c r="Q138" s="2"/>
       <c r="R138" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="S138" t="s" s="2">
         <v>77</v>
@@ -17970,7 +17963,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>87</v>
@@ -17999,10 +17992,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18028,10 +18021,10 @@
         <v>239</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18082,7 +18075,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18111,13 +18104,13 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>77</v>
@@ -18196,7 +18189,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18225,10 +18218,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18251,13 +18244,13 @@
         <v>77</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18308,7 +18301,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18326,7 +18319,7 @@
         <v>77</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>77</v>
@@ -18337,10 +18330,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18411,7 +18404,7 @@
         <v>135</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>77</v>
@@ -18420,7 +18413,7 @@
         <v>136</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18449,10 +18442,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18478,13 +18471,13 @@
         <v>101</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -18492,7 +18485,7 @@
       </c>
       <c r="Q143" s="2"/>
       <c r="R143" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="S143" t="s" s="2">
         <v>77</v>
@@ -18534,7 +18527,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>87</v>
@@ -18563,10 +18556,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18589,13 +18582,13 @@
         <v>77</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -18646,7 +18639,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -18675,10 +18668,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18704,13 +18697,13 @@
         <v>101</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -18718,7 +18711,7 @@
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>77</v>
@@ -18760,7 +18753,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>87</v>
@@ -18789,10 +18782,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18815,13 +18808,13 @@
         <v>77</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -18872,7 +18865,7 @@
         <v>77</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -18901,10 +18894,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18927,16 +18920,16 @@
         <v>88</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -18986,7 +18979,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -18995,7 +18988,7 @@
         <v>87</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>99</v>
@@ -19015,10 +19008,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19044,13 +19037,13 @@
         <v>101</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N148" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19076,31 +19069,31 @@
         <v>77</v>
       </c>
       <c r="X148" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="Z148" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="Y148" t="s" s="2">
+      <c r="AA148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF148" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19129,10 +19122,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19158,13 +19151,13 @@
         <v>187</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19214,7 +19207,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19232,7 +19225,7 @@
         <v>77</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>77</v>
@@ -19243,10 +19236,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19269,16 +19262,16 @@
         <v>88</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N150" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19328,7 +19321,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19357,10 +19350,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19383,17 +19376,17 @@
         <v>77</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -19442,7 +19435,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19460,7 +19453,7 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
@@ -19471,10 +19464,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19497,17 +19490,17 @@
         <v>88</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>77</v>
@@ -19556,7 +19549,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19574,10 +19567,10 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>77</v>
@@ -19585,10 +19578,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19614,13 +19607,13 @@
         <v>239</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N153" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -19649,10 +19642,10 @@
         <v>243</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>77</v>
@@ -19670,7 +19663,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -19685,13 +19678,13 @@
         <v>99</v>
       </c>
       <c r="AK153" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM153" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>77</v>
@@ -19699,10 +19692,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19725,16 +19718,16 @@
         <v>88</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -19784,7 +19777,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -19799,13 +19792,13 @@
         <v>99</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>77</v>
@@ -19813,10 +19806,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19842,13 +19835,13 @@
         <v>239</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N155" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -19878,7 +19871,7 @@
       </c>
       <c r="Y155" s="2"/>
       <c r="Z155" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>77</v>
@@ -19896,7 +19889,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -19914,21 +19907,21 @@
         <v>77</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19951,13 +19944,13 @@
         <v>77</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -20008,7 +20001,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20026,7 +20019,7 @@
         <v>77</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>77</v>
@@ -20037,10 +20030,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20066,10 +20059,10 @@
         <v>132</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N157" t="s" s="2">
         <v>183</v>
@@ -20113,7 +20106,7 @@
         <v>135</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>77</v>
@@ -20122,7 +20115,7 @@
         <v>136</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20140,7 +20133,7 @@
         <v>77</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>77</v>
@@ -20151,13 +20144,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B158" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C158" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="C158" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="D158" t="s" s="2">
         <v>77</v>
@@ -20179,13 +20172,13 @@
         <v>77</v>
       </c>
       <c r="K158" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -20236,7 +20229,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20265,10 +20258,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20291,13 +20284,13 @@
         <v>77</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -20348,7 +20341,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20357,7 +20350,7 @@
         <v>87</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>77</v>
@@ -20366,7 +20359,7 @@
         <v>77</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>77</v>
@@ -20377,10 +20370,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20451,7 +20444,7 @@
         <v>135</v>
       </c>
       <c r="AC160" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD160" t="s" s="2">
         <v>77</v>
@@ -20460,7 +20453,7 @@
         <v>136</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20489,10 +20482,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20518,13 +20511,13 @@
         <v>101</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -20532,7 +20525,7 @@
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>77</v>
@@ -20574,7 +20567,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>87</v>
@@ -20603,10 +20596,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20629,13 +20622,13 @@
         <v>77</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -20686,7 +20679,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -20695,7 +20688,7 @@
         <v>87</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>99</v>
@@ -20715,10 +20708,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20741,19 +20734,19 @@
         <v>88</v>
       </c>
       <c r="K163" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L163" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="L163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="O163" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>77</v>
@@ -20802,7 +20795,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -20820,21 +20813,21 @@
         <v>77</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20857,19 +20850,19 @@
         <v>88</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N164" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>77</v>
@@ -20918,7 +20911,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -20936,21 +20929,21 @@
         <v>77</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20976,13 +20969,13 @@
         <v>239</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N165" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -21011,10 +21004,10 @@
         <v>243</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>77</v>
@@ -21032,7 +21025,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -21050,7 +21043,7 @@
         <v>77</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>77</v>
@@ -21061,10 +21054,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21087,16 +21080,16 @@
         <v>77</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="L166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -21146,7 +21139,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -21164,7 +21157,7 @@
         <v>77</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>77</v>
@@ -21175,10 +21168,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21204,13 +21197,13 @@
         <v>239</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -21239,10 +21232,10 @@
         <v>243</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>77</v>
@@ -21260,7 +21253,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -21278,7 +21271,7 @@
         <v>77</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>77</v>
@@ -21289,10 +21282,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21315,13 +21308,13 @@
         <v>77</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -21372,7 +21365,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -21390,7 +21383,7 @@
         <v>77</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>77</v>
@@ -21401,10 +21394,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21430,10 +21423,10 @@
         <v>132</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>183</v>
@@ -21477,7 +21470,7 @@
         <v>135</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>77</v>
@@ -21486,7 +21479,7 @@
         <v>136</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -21504,7 +21497,7 @@
         <v>77</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>77</v>
@@ -21515,10 +21508,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21541,19 +21534,19 @@
         <v>88</v>
       </c>
       <c r="K170" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="L170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="O170" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>77</v>
@@ -21602,7 +21595,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -21620,21 +21613,21 @@
         <v>77</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21657,19 +21650,19 @@
         <v>88</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="M171" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O171" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>77</v>
@@ -21718,7 +21711,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -21736,21 +21729,21 @@
         <v>77</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21773,17 +21766,17 @@
         <v>77</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="L172" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>77</v>
@@ -21832,7 +21825,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -21850,7 +21843,7 @@
         <v>77</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>77</v>
@@ -21861,10 +21854,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21890,10 +21883,10 @@
         <v>239</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -21923,10 +21916,10 @@
         <v>243</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>77</v>
@@ -21944,7 +21937,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -21962,7 +21955,7 @@
         <v>77</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>77</v>
@@ -21973,10 +21966,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21999,13 +21992,13 @@
         <v>77</v>
       </c>
       <c r="K174" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="L174" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -22056,7 +22049,7 @@
         <v>77</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>78</v>
@@ -22071,24 +22064,24 @@
         <v>99</v>
       </c>
       <c r="AK174" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AL174" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AM174" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN174" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AL174" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AM174" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN174" t="s" s="2">
-        <v>623</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22111,13 +22104,13 @@
         <v>77</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -22168,7 +22161,7 @@
         <v>77</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>78</v>
@@ -22186,7 +22179,7 @@
         <v>77</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>77</v>
@@ -22197,10 +22190,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22223,13 +22216,13 @@
         <v>77</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -22280,7 +22273,7 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>78</v>
@@ -22298,7 +22291,7 @@
         <v>77</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>77</v>
@@ -22309,10 +22302,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22338,10 +22331,10 @@
         <v>132</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N177" t="s" s="2">
         <v>183</v>
@@ -22394,7 +22387,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>
@@ -22412,7 +22405,7 @@
         <v>77</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>77</v>
@@ -22423,14 +22416,14 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
@@ -22452,10 +22445,10 @@
         <v>132</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="N178" t="s" s="2">
         <v>183</v>
@@ -22510,7 +22503,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>78</v>
@@ -22539,10 +22532,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22568,10 +22561,10 @@
         <v>239</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -22601,10 +22594,10 @@
         <v>111</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>77</v>
@@ -22622,7 +22615,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>78</v>
@@ -22640,7 +22633,7 @@
         <v>77</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>77</v>
@@ -22651,10 +22644,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22677,13 +22670,13 @@
         <v>77</v>
       </c>
       <c r="K180" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="L180" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M180" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="L180" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -22734,7 +22727,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>87</v>
@@ -22752,7 +22745,7 @@
         <v>77</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>77</v>
@@ -22763,10 +22756,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22789,19 +22782,19 @@
         <v>77</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M181" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N181" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="O181" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>77</v>
@@ -22850,7 +22843,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>
@@ -22868,7 +22861,7 @@
         <v>77</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AM181" t="s" s="2">
         <v>77</v>
@@ -22879,10 +22872,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -22908,13 +22901,13 @@
         <v>239</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -22943,10 +22936,10 @@
         <v>243</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>77</v>
@@ -22964,7 +22957,7 @@
         <v>77</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>78</v>
@@ -22982,7 +22975,7 @@
         <v>77</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
